--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/UTAH_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/UTAH_2012.xlsx
@@ -643,7 +643,7 @@
         <v>132</v>
       </c>
       <c r="D16">
-        <v>0.009062821833162</v>
+        <v>0.009062821833162002</v>
       </c>
     </row>
     <row r="17">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C109">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C178">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C678">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C749">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C750">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C768">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1087">
@@ -21858,7 +21858,7 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1195">
